--- a/fix-errors/ig/FRHeaderDocumentLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRHeaderDocumentLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -110,13 +110,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-header-document</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-header-document|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-clinical-document</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-clinical-document|0.1.0</t>
   </si>
   <si>
     <t>FRLMHeaderDocument</t>
@@ -260,13 +260,13 @@
     <t>ClinicalDocument.componentOf</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-bundle-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-bundle-document|0.1.0</t>
   </si>
   <si>
     <t>Bundle.identifier</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>Composition.type</t>
